--- a/CPRD Raw Analysis/Results/SecondaryCareAnalysis/AE/Output_AE_attdances_Raw.xlsx
+++ b/CPRD Raw Analysis/Results/SecondaryCareAnalysis/AE/Output_AE_attdances_Raw.xlsx
@@ -417,34 +417,34 @@
         <v>15628</v>
       </c>
       <c r="B2">
-        <v>1.86</v>
+        <v>24.52</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>80</v>
+        <v>1848</v>
       </c>
       <c r="E2">
-        <v>1.64</v>
+        <v>51.18</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="I2">
-        <v>0.01</v>
+        <v>0.41</v>
       </c>
       <c r="J2">
-        <v>1.83</v>
+        <v>23.72</v>
       </c>
       <c r="K2">
-        <v>1.88</v>
+        <v>25.33</v>
       </c>
     </row>
   </sheetData>
@@ -519,34 +519,34 @@
         <v>23106</v>
       </c>
       <c r="B2">
-        <v>1.25</v>
+        <v>16.59</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>80</v>
+        <v>1848</v>
       </c>
       <c r="E2">
-        <v>1.61</v>
+        <v>43.62</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="I2">
-        <v>0.01</v>
+        <v>0.29</v>
       </c>
       <c r="J2">
-        <v>1.23</v>
+        <v>16.02</v>
       </c>
       <c r="K2">
-        <v>1.28</v>
+        <v>17.15</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/SecondaryCareAnalysis/AE/Output_AE_attdances_Raw.xlsx
+++ b/CPRD Raw Analysis/Results/SecondaryCareAnalysis/AE/Output_AE_attdances_Raw.xlsx
@@ -417,34 +417,34 @@
         <v>15628</v>
       </c>
       <c r="B2">
-        <v>24.52</v>
+        <v>6.09</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>1848</v>
+        <v>245</v>
       </c>
       <c r="E2">
-        <v>51.18</v>
+        <v>6.58</v>
       </c>
       <c r="F2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="I2">
-        <v>0.41</v>
+        <v>0.05</v>
       </c>
       <c r="J2">
-        <v>23.72</v>
+        <v>5.99</v>
       </c>
       <c r="K2">
-        <v>25.33</v>
+        <v>6.2</v>
       </c>
     </row>
   </sheetData>
@@ -519,34 +519,34 @@
         <v>23106</v>
       </c>
       <c r="B2">
-        <v>16.59</v>
+        <v>4.12</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>1848</v>
+        <v>245</v>
       </c>
       <c r="E2">
-        <v>43.62</v>
+        <v>6.12</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="I2">
-        <v>0.29</v>
+        <v>0.04</v>
       </c>
       <c r="J2">
-        <v>16.02</v>
+        <v>4.04</v>
       </c>
       <c r="K2">
-        <v>17.15</v>
+        <v>4.2</v>
       </c>
     </row>
   </sheetData>
